--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:11</t>
+    <t xml:space="preserve">2026-09-09 19:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:44</t>
+    <t xml:space="preserve">2026-09-17 04:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:08</t>
+    <t xml:space="preserve">2026-09-27 02:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:37</t>
+    <t xml:space="preserve">2026-10-03 01:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_nuble.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">apoyo</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 01:46</t>
+    <t xml:space="preserve">2026-10-05 05:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Nuble</t>
+    <t xml:space="preserve">Region de Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
